--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-kanal.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-ekg-kanal.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Unknown region code '276'</t>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>
@@ -1089,7 +1089,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-objekte-geraete-mdc|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-objekte-geraete-mdc|2027.0.0-ballot</t>
   </si>
   <si>
     <t>Device.type.coding:geraetetyp.id</t>
@@ -1372,7 +1372,7 @@
     <t>Device.property:kanalbezeichnung.valueCode</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-ekg-kanaele-mdc|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-ekg-kanaele-mdc|2027.0.0-ballot</t>
   </si>
   <si>
     <t>Device.patient</t>
@@ -1500,7 +1500,7 @@
     <t>Device.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/StructureDefinition/mii-pr-kardio-ekg-geraet|2027.0.0-ballot.rc1)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/StructureDefinition/mii-pr-kardio-ekg-geraet|2027.0.0-ballot)
 </t>
   </si>
   <si>
@@ -1839,7 +1839,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="112.1796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="109.171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1854,7 +1854,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="36.078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="103.0078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="100.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
